--- a/artfynd/A 26837-2025 artfynd.xlsx
+++ b/artfynd/A 26837-2025 artfynd.xlsx
@@ -2342,32 +2342,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129099751</v>
+        <v>129099758</v>
       </c>
       <c r="B18" t="n">
-        <v>57827</v>
+        <v>78700</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103031</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>672101</v>
+        <v>672113</v>
       </c>
       <c r="R18" t="n">
-        <v>7394668</v>
+        <v>7394667</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2413,11 +2413,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2444,32 +2439,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129099758</v>
+        <v>129099751</v>
       </c>
       <c r="B19" t="n">
-        <v>78700</v>
+        <v>57827</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>353</v>
+        <v>103031</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2479,10 +2474,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>672113</v>
+        <v>672101</v>
       </c>
       <c r="R19" t="n">
-        <v>7394667</v>
+        <v>7394668</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2515,6 +2510,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 26837-2025 artfynd.xlsx
+++ b/artfynd/A 26837-2025 artfynd.xlsx
@@ -1472,7 +1472,7 @@
         <v>129099750</v>
       </c>
       <c r="B9" t="n">
-        <v>93006</v>
+        <v>93011</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1663,32 +1663,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129099746</v>
+        <v>129099755</v>
       </c>
       <c r="B11" t="n">
-        <v>90552</v>
+        <v>91784</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1962</v>
+        <v>65</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>672131</v>
+        <v>671997</v>
       </c>
       <c r="R11" t="n">
-        <v>7394641</v>
+        <v>7394521</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1760,32 +1760,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129099755</v>
+        <v>129099760</v>
       </c>
       <c r="B12" t="n">
-        <v>91781</v>
+        <v>78700</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>65</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1795,10 +1795,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>671997</v>
+        <v>671996</v>
       </c>
       <c r="R12" t="n">
-        <v>7394521</v>
+        <v>7394503</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1857,7 +1857,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129099760</v>
+        <v>129099756</v>
       </c>
       <c r="B13" t="n">
         <v>78700</v>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>671996</v>
+        <v>672148</v>
       </c>
       <c r="R13" t="n">
-        <v>7394503</v>
+        <v>7394634</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1954,10 +1954,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129099756</v>
+        <v>129099746</v>
       </c>
       <c r="B14" t="n">
-        <v>78700</v>
+        <v>90555</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1965,21 +1965,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>1962</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>672148</v>
+        <v>672131</v>
       </c>
       <c r="R14" t="n">
-        <v>7394634</v>
+        <v>7394641</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2054,7 +2054,7 @@
         <v>129099749</v>
       </c>
       <c r="B15" t="n">
-        <v>97528</v>
+        <v>97533</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>129099753</v>
       </c>
       <c r="B16" t="n">
-        <v>91681</v>
+        <v>91684</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>129099745</v>
       </c>
       <c r="B17" t="n">
-        <v>91442</v>
+        <v>91445</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
         <v>129099754</v>
       </c>
       <c r="B20" t="n">
-        <v>91781</v>
+        <v>91784</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 26837-2025 artfynd.xlsx
+++ b/artfynd/A 26837-2025 artfynd.xlsx
@@ -1472,7 +1472,7 @@
         <v>129099750</v>
       </c>
       <c r="B9" t="n">
-        <v>93011</v>
+        <v>93014</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>129099761</v>
       </c>
       <c r="B10" t="n">
-        <v>78437</v>
+        <v>78438</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>129099755</v>
       </c>
       <c r="B11" t="n">
-        <v>91784</v>
+        <v>91787</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1760,10 +1760,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129099760</v>
+        <v>129099756</v>
       </c>
       <c r="B12" t="n">
-        <v>78700</v>
+        <v>78701</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1795,10 +1795,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>671996</v>
+        <v>672148</v>
       </c>
       <c r="R12" t="n">
-        <v>7394503</v>
+        <v>7394634</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1857,10 +1857,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129099756</v>
+        <v>129099760</v>
       </c>
       <c r="B13" t="n">
-        <v>78700</v>
+        <v>78701</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>672148</v>
+        <v>671996</v>
       </c>
       <c r="R13" t="n">
-        <v>7394634</v>
+        <v>7394503</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1957,7 +1957,7 @@
         <v>129099746</v>
       </c>
       <c r="B14" t="n">
-        <v>90555</v>
+        <v>90558</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>129099749</v>
       </c>
       <c r="B15" t="n">
-        <v>97533</v>
+        <v>97536</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>129099753</v>
       </c>
       <c r="B16" t="n">
-        <v>91684</v>
+        <v>91687</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>129099745</v>
       </c>
       <c r="B17" t="n">
-        <v>91445</v>
+        <v>91448</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>129099758</v>
       </c>
       <c r="B18" t="n">
-        <v>78700</v>
+        <v>78701</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
         <v>129099754</v>
       </c>
       <c r="B20" t="n">
-        <v>91784</v>
+        <v>91787</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>129099759</v>
       </c>
       <c r="B21" t="n">
-        <v>78700</v>
+        <v>78701</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 26837-2025 artfynd.xlsx
+++ b/artfynd/A 26837-2025 artfynd.xlsx
@@ -1663,32 +1663,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129099755</v>
+        <v>129099749</v>
       </c>
       <c r="B11" t="n">
-        <v>91787</v>
+        <v>97536</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>65</v>
+        <v>221941</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>671997</v>
+        <v>672300</v>
       </c>
       <c r="R11" t="n">
-        <v>7394521</v>
+        <v>7394545</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1760,32 +1760,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129099756</v>
+        <v>129099755</v>
       </c>
       <c r="B12" t="n">
-        <v>78701</v>
+        <v>91787</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>65</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1795,10 +1795,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>672148</v>
+        <v>671997</v>
       </c>
       <c r="R12" t="n">
-        <v>7394634</v>
+        <v>7394521</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1954,10 +1954,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129099746</v>
+        <v>129099756</v>
       </c>
       <c r="B14" t="n">
-        <v>90558</v>
+        <v>78701</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1965,21 +1965,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>672131</v>
+        <v>672148</v>
       </c>
       <c r="R14" t="n">
-        <v>7394641</v>
+        <v>7394634</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2051,32 +2051,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129099749</v>
+        <v>129099746</v>
       </c>
       <c r="B15" t="n">
-        <v>97536</v>
+        <v>90558</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221941</v>
+        <v>1962</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2086,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>672300</v>
+        <v>672131</v>
       </c>
       <c r="R15" t="n">
-        <v>7394545</v>
+        <v>7394641</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2342,32 +2342,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129099758</v>
+        <v>129099751</v>
       </c>
       <c r="B18" t="n">
-        <v>78701</v>
+        <v>57827</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>103031</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>672113</v>
+        <v>672101</v>
       </c>
       <c r="R18" t="n">
-        <v>7394667</v>
+        <v>7394668</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2413,6 +2413,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2439,32 +2444,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129099751</v>
+        <v>129099758</v>
       </c>
       <c r="B19" t="n">
-        <v>57827</v>
+        <v>78701</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103031</v>
+        <v>353</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2474,10 +2479,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>672101</v>
+        <v>672113</v>
       </c>
       <c r="R19" t="n">
-        <v>7394668</v>
+        <v>7394667</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2510,11 +2515,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 26837-2025 artfynd.xlsx
+++ b/artfynd/A 26837-2025 artfynd.xlsx
@@ -1663,32 +1663,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129099749</v>
+        <v>129099755</v>
       </c>
       <c r="B11" t="n">
-        <v>97536</v>
+        <v>91787</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221941</v>
+        <v>65</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>672300</v>
+        <v>671997</v>
       </c>
       <c r="R11" t="n">
-        <v>7394545</v>
+        <v>7394521</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1760,32 +1760,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129099755</v>
+        <v>129099760</v>
       </c>
       <c r="B12" t="n">
-        <v>91787</v>
+        <v>78701</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>65</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1795,10 +1795,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>671997</v>
+        <v>671996</v>
       </c>
       <c r="R12" t="n">
-        <v>7394521</v>
+        <v>7394503</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1857,7 +1857,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129099760</v>
+        <v>129099756</v>
       </c>
       <c r="B13" t="n">
         <v>78701</v>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>671996</v>
+        <v>672148</v>
       </c>
       <c r="R13" t="n">
-        <v>7394503</v>
+        <v>7394634</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1954,10 +1954,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129099756</v>
+        <v>129099746</v>
       </c>
       <c r="B14" t="n">
-        <v>78701</v>
+        <v>90558</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1965,21 +1965,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>1962</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>672148</v>
+        <v>672131</v>
       </c>
       <c r="R14" t="n">
-        <v>7394634</v>
+        <v>7394641</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2051,32 +2051,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129099746</v>
+        <v>129099749</v>
       </c>
       <c r="B15" t="n">
-        <v>90558</v>
+        <v>97536</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1962</v>
+        <v>221941</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2086,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>672131</v>
+        <v>672300</v>
       </c>
       <c r="R15" t="n">
-        <v>7394641</v>
+        <v>7394545</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2342,32 +2342,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129099751</v>
+        <v>129099758</v>
       </c>
       <c r="B18" t="n">
-        <v>57827</v>
+        <v>78701</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103031</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>672101</v>
+        <v>672113</v>
       </c>
       <c r="R18" t="n">
-        <v>7394668</v>
+        <v>7394667</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2413,11 +2413,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2444,32 +2439,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129099758</v>
+        <v>129099751</v>
       </c>
       <c r="B19" t="n">
-        <v>78701</v>
+        <v>57827</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>353</v>
+        <v>103031</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2479,10 +2474,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>672113</v>
+        <v>672101</v>
       </c>
       <c r="R19" t="n">
-        <v>7394667</v>
+        <v>7394668</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2515,6 +2510,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 26837-2025 artfynd.xlsx
+++ b/artfynd/A 26837-2025 artfynd.xlsx
@@ -1472,7 +1472,7 @@
         <v>129099750</v>
       </c>
       <c r="B9" t="n">
-        <v>93014</v>
+        <v>93022</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>129099761</v>
       </c>
       <c r="B10" t="n">
-        <v>78438</v>
+        <v>78442</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1663,32 +1663,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129099755</v>
+        <v>129099749</v>
       </c>
       <c r="B11" t="n">
-        <v>91787</v>
+        <v>97546</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>65</v>
+        <v>221941</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>671997</v>
+        <v>672300</v>
       </c>
       <c r="R11" t="n">
-        <v>7394521</v>
+        <v>7394545</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1760,32 +1760,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129099760</v>
+        <v>129099755</v>
       </c>
       <c r="B12" t="n">
-        <v>78701</v>
+        <v>91794</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>65</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1795,10 +1795,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>671996</v>
+        <v>671997</v>
       </c>
       <c r="R12" t="n">
-        <v>7394503</v>
+        <v>7394521</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1860,7 +1860,7 @@
         <v>129099756</v>
       </c>
       <c r="B13" t="n">
-        <v>78701</v>
+        <v>78705</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1954,10 +1954,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129099746</v>
+        <v>129099760</v>
       </c>
       <c r="B14" t="n">
-        <v>90558</v>
+        <v>78705</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1965,21 +1965,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>672131</v>
+        <v>671996</v>
       </c>
       <c r="R14" t="n">
-        <v>7394641</v>
+        <v>7394503</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2051,32 +2051,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129099749</v>
+        <v>129099746</v>
       </c>
       <c r="B15" t="n">
-        <v>97536</v>
+        <v>90562</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221941</v>
+        <v>1962</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2086,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>672300</v>
+        <v>672131</v>
       </c>
       <c r="R15" t="n">
-        <v>7394545</v>
+        <v>7394641</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2151,7 +2151,7 @@
         <v>129099753</v>
       </c>
       <c r="B16" t="n">
-        <v>91687</v>
+        <v>91694</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>129099745</v>
       </c>
       <c r="B17" t="n">
-        <v>91448</v>
+        <v>91454</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>129099758</v>
       </c>
       <c r="B18" t="n">
-        <v>78701</v>
+        <v>78705</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>129099751</v>
       </c>
       <c r="B19" t="n">
-        <v>57827</v>
+        <v>57829</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
         <v>129099754</v>
       </c>
       <c r="B20" t="n">
-        <v>91787</v>
+        <v>91794</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>129099759</v>
       </c>
       <c r="B21" t="n">
-        <v>78701</v>
+        <v>78705</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 26837-2025 artfynd.xlsx
+++ b/artfynd/A 26837-2025 artfynd.xlsx
@@ -1472,7 +1472,7 @@
         <v>129099750</v>
       </c>
       <c r="B9" t="n">
-        <v>93022</v>
+        <v>93029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1663,32 +1663,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129099749</v>
+        <v>129099755</v>
       </c>
       <c r="B11" t="n">
-        <v>97546</v>
+        <v>91801</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221941</v>
+        <v>65</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>672300</v>
+        <v>671997</v>
       </c>
       <c r="R11" t="n">
-        <v>7394545</v>
+        <v>7394521</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1760,32 +1760,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129099755</v>
+        <v>129099756</v>
       </c>
       <c r="B12" t="n">
-        <v>91794</v>
+        <v>78705</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>65</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1795,10 +1795,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>671997</v>
+        <v>672148</v>
       </c>
       <c r="R12" t="n">
-        <v>7394521</v>
+        <v>7394634</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1857,7 +1857,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129099756</v>
+        <v>129099760</v>
       </c>
       <c r="B13" t="n">
         <v>78705</v>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>672148</v>
+        <v>671996</v>
       </c>
       <c r="R13" t="n">
-        <v>7394634</v>
+        <v>7394503</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1954,10 +1954,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129099760</v>
+        <v>129099746</v>
       </c>
       <c r="B14" t="n">
-        <v>78705</v>
+        <v>90569</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1965,21 +1965,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>1962</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>671996</v>
+        <v>672131</v>
       </c>
       <c r="R14" t="n">
-        <v>7394503</v>
+        <v>7394641</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2051,32 +2051,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129099746</v>
+        <v>129099749</v>
       </c>
       <c r="B15" t="n">
-        <v>90562</v>
+        <v>97553</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1962</v>
+        <v>221941</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2086,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>672131</v>
+        <v>672300</v>
       </c>
       <c r="R15" t="n">
-        <v>7394641</v>
+        <v>7394545</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2148,32 +2148,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129099753</v>
+        <v>129099745</v>
       </c>
       <c r="B16" t="n">
-        <v>91694</v>
+        <v>91461</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1503</v>
+        <v>3242</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2183,10 +2183,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>672237</v>
+        <v>672062</v>
       </c>
       <c r="R16" t="n">
-        <v>7394626</v>
+        <v>7394679</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2245,32 +2245,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129099745</v>
+        <v>129099753</v>
       </c>
       <c r="B17" t="n">
-        <v>91454</v>
+        <v>91701</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3242</v>
+        <v>1503</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>672062</v>
+        <v>672237</v>
       </c>
       <c r="R17" t="n">
-        <v>7394679</v>
+        <v>7394626</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2544,7 +2544,7 @@
         <v>129099754</v>
       </c>
       <c r="B20" t="n">
-        <v>91794</v>
+        <v>91801</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 26837-2025 artfynd.xlsx
+++ b/artfynd/A 26837-2025 artfynd.xlsx
@@ -1472,7 +1472,7 @@
         <v>129099750</v>
       </c>
       <c r="B9" t="n">
-        <v>93029</v>
+        <v>93031</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>129099761</v>
       </c>
       <c r="B10" t="n">
-        <v>78442</v>
+        <v>78444</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>129099755</v>
       </c>
       <c r="B11" t="n">
-        <v>91801</v>
+        <v>91803</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1760,10 +1760,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129099756</v>
+        <v>129099760</v>
       </c>
       <c r="B12" t="n">
-        <v>78705</v>
+        <v>78707</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1795,10 +1795,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>672148</v>
+        <v>671996</v>
       </c>
       <c r="R12" t="n">
-        <v>7394634</v>
+        <v>7394503</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1857,10 +1857,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129099760</v>
+        <v>129099756</v>
       </c>
       <c r="B13" t="n">
-        <v>78705</v>
+        <v>78707</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>671996</v>
+        <v>672148</v>
       </c>
       <c r="R13" t="n">
-        <v>7394503</v>
+        <v>7394634</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1954,32 +1954,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129099746</v>
+        <v>129099749</v>
       </c>
       <c r="B14" t="n">
-        <v>90569</v>
+        <v>97555</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1962</v>
+        <v>221941</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>672131</v>
+        <v>672300</v>
       </c>
       <c r="R14" t="n">
-        <v>7394641</v>
+        <v>7394545</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2051,32 +2051,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129099749</v>
+        <v>129099746</v>
       </c>
       <c r="B15" t="n">
-        <v>97553</v>
+        <v>90571</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221941</v>
+        <v>1962</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2086,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>672300</v>
+        <v>672131</v>
       </c>
       <c r="R15" t="n">
-        <v>7394545</v>
+        <v>7394641</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2148,32 +2148,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129099745</v>
+        <v>129099753</v>
       </c>
       <c r="B16" t="n">
-        <v>91461</v>
+        <v>91703</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3242</v>
+        <v>1503</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2183,10 +2183,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>672062</v>
+        <v>672237</v>
       </c>
       <c r="R16" t="n">
-        <v>7394679</v>
+        <v>7394626</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2245,32 +2245,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129099753</v>
+        <v>129099745</v>
       </c>
       <c r="B17" t="n">
-        <v>91701</v>
+        <v>91463</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1503</v>
+        <v>3242</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>672237</v>
+        <v>672062</v>
       </c>
       <c r="R17" t="n">
-        <v>7394626</v>
+        <v>7394679</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2345,7 +2345,7 @@
         <v>129099758</v>
       </c>
       <c r="B18" t="n">
-        <v>78705</v>
+        <v>78707</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>129099751</v>
       </c>
       <c r="B19" t="n">
-        <v>57829</v>
+        <v>57831</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
         <v>129099754</v>
       </c>
       <c r="B20" t="n">
-        <v>91801</v>
+        <v>91803</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>129099759</v>
       </c>
       <c r="B21" t="n">
-        <v>78705</v>
+        <v>78707</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 26837-2025 artfynd.xlsx
+++ b/artfynd/A 26837-2025 artfynd.xlsx
@@ -1954,32 +1954,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129099749</v>
+        <v>129099746</v>
       </c>
       <c r="B14" t="n">
-        <v>97555</v>
+        <v>90571</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221941</v>
+        <v>1962</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>672300</v>
+        <v>672131</v>
       </c>
       <c r="R14" t="n">
-        <v>7394545</v>
+        <v>7394641</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2051,32 +2051,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129099746</v>
+        <v>129099749</v>
       </c>
       <c r="B15" t="n">
-        <v>90571</v>
+        <v>97555</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1962</v>
+        <v>221941</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2086,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>672131</v>
+        <v>672300</v>
       </c>
       <c r="R15" t="n">
-        <v>7394641</v>
+        <v>7394545</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>

--- a/artfynd/A 26837-2025 artfynd.xlsx
+++ b/artfynd/A 26837-2025 artfynd.xlsx
@@ -1663,32 +1663,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129099755</v>
+        <v>129099756</v>
       </c>
       <c r="B11" t="n">
-        <v>91803</v>
+        <v>78707</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>65</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>671997</v>
+        <v>672148</v>
       </c>
       <c r="R11" t="n">
-        <v>7394521</v>
+        <v>7394634</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1760,10 +1760,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129099760</v>
+        <v>129099746</v>
       </c>
       <c r="B12" t="n">
-        <v>78707</v>
+        <v>90571</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1771,21 +1771,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>1962</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1795,10 +1795,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>671996</v>
+        <v>672131</v>
       </c>
       <c r="R12" t="n">
-        <v>7394503</v>
+        <v>7394641</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1857,32 +1857,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129099756</v>
+        <v>129099755</v>
       </c>
       <c r="B13" t="n">
-        <v>78707</v>
+        <v>91803</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>65</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>672148</v>
+        <v>671997</v>
       </c>
       <c r="R13" t="n">
-        <v>7394634</v>
+        <v>7394521</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1954,10 +1954,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129099746</v>
+        <v>129099760</v>
       </c>
       <c r="B14" t="n">
-        <v>90571</v>
+        <v>78707</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1965,21 +1965,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>672131</v>
+        <v>671996</v>
       </c>
       <c r="R14" t="n">
-        <v>7394641</v>
+        <v>7394503</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>

--- a/artfynd/A 26837-2025 artfynd.xlsx
+++ b/artfynd/A 26837-2025 artfynd.xlsx
@@ -1472,7 +1472,7 @@
         <v>129099750</v>
       </c>
       <c r="B9" t="n">
-        <v>93031</v>
+        <v>91592</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1663,32 +1663,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129099756</v>
+        <v>129099749</v>
       </c>
       <c r="B11" t="n">
-        <v>78707</v>
+        <v>97581</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>221941</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>672148</v>
+        <v>672300</v>
       </c>
       <c r="R11" t="n">
-        <v>7394634</v>
+        <v>7394545</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1760,32 +1760,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129099746</v>
+        <v>129099755</v>
       </c>
       <c r="B12" t="n">
-        <v>90571</v>
+        <v>91812</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1962</v>
+        <v>65</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1795,10 +1795,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>672131</v>
+        <v>671997</v>
       </c>
       <c r="R12" t="n">
-        <v>7394641</v>
+        <v>7394521</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1857,32 +1857,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129099755</v>
+        <v>129099760</v>
       </c>
       <c r="B13" t="n">
-        <v>91803</v>
+        <v>78707</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>65</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>671997</v>
+        <v>671996</v>
       </c>
       <c r="R13" t="n">
-        <v>7394521</v>
+        <v>7394503</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1954,7 +1954,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129099760</v>
+        <v>129099756</v>
       </c>
       <c r="B14" t="n">
         <v>78707</v>
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>671996</v>
+        <v>672148</v>
       </c>
       <c r="R14" t="n">
-        <v>7394503</v>
+        <v>7394634</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2051,32 +2051,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129099749</v>
+        <v>129099746</v>
       </c>
       <c r="B15" t="n">
-        <v>97555</v>
+        <v>90572</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221941</v>
+        <v>1962</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2086,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>672300</v>
+        <v>672131</v>
       </c>
       <c r="R15" t="n">
-        <v>7394545</v>
+        <v>7394641</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2148,32 +2148,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129099753</v>
+        <v>129099745</v>
       </c>
       <c r="B16" t="n">
-        <v>91703</v>
+        <v>91463</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1503</v>
+        <v>3242</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2183,10 +2183,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>672237</v>
+        <v>672062</v>
       </c>
       <c r="R16" t="n">
-        <v>7394626</v>
+        <v>7394679</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2245,32 +2245,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129099745</v>
+        <v>129099753</v>
       </c>
       <c r="B17" t="n">
-        <v>91463</v>
+        <v>91712</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3242</v>
+        <v>1503</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>672062</v>
+        <v>672237</v>
       </c>
       <c r="R17" t="n">
-        <v>7394679</v>
+        <v>7394626</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2544,7 +2544,7 @@
         <v>129099754</v>
       </c>
       <c r="B20" t="n">
-        <v>91803</v>
+        <v>91812</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 26837-2025 artfynd.xlsx
+++ b/artfynd/A 26837-2025 artfynd.xlsx
@@ -1472,7 +1472,7 @@
         <v>129099750</v>
       </c>
       <c r="B9" t="n">
-        <v>91592</v>
+        <v>91593</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1663,32 +1663,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129099749</v>
+        <v>129099755</v>
       </c>
       <c r="B11" t="n">
-        <v>97581</v>
+        <v>91813</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221941</v>
+        <v>65</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>672300</v>
+        <v>671997</v>
       </c>
       <c r="R11" t="n">
-        <v>7394545</v>
+        <v>7394521</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1760,32 +1760,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129099755</v>
+        <v>129099760</v>
       </c>
       <c r="B12" t="n">
-        <v>91812</v>
+        <v>78707</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>65</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1795,10 +1795,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>671997</v>
+        <v>671996</v>
       </c>
       <c r="R12" t="n">
-        <v>7394521</v>
+        <v>7394503</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1857,7 +1857,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129099760</v>
+        <v>129099756</v>
       </c>
       <c r="B13" t="n">
         <v>78707</v>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>671996</v>
+        <v>672148</v>
       </c>
       <c r="R13" t="n">
-        <v>7394503</v>
+        <v>7394634</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1954,10 +1954,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129099756</v>
+        <v>129099746</v>
       </c>
       <c r="B14" t="n">
-        <v>78707</v>
+        <v>90572</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1965,21 +1965,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>1962</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>672148</v>
+        <v>672131</v>
       </c>
       <c r="R14" t="n">
-        <v>7394634</v>
+        <v>7394641</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2051,32 +2051,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129099746</v>
+        <v>129099749</v>
       </c>
       <c r="B15" t="n">
-        <v>90572</v>
+        <v>97582</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1962</v>
+        <v>221941</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2086,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>672131</v>
+        <v>672300</v>
       </c>
       <c r="R15" t="n">
-        <v>7394641</v>
+        <v>7394545</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2148,32 +2148,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129099745</v>
+        <v>129099753</v>
       </c>
       <c r="B16" t="n">
-        <v>91463</v>
+        <v>91713</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3242</v>
+        <v>1503</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2183,10 +2183,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>672062</v>
+        <v>672237</v>
       </c>
       <c r="R16" t="n">
-        <v>7394679</v>
+        <v>7394626</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2245,32 +2245,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129099753</v>
+        <v>129099745</v>
       </c>
       <c r="B17" t="n">
-        <v>91712</v>
+        <v>91463</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1503</v>
+        <v>3242</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>672237</v>
+        <v>672062</v>
       </c>
       <c r="R17" t="n">
-        <v>7394626</v>
+        <v>7394679</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2544,7 +2544,7 @@
         <v>129099754</v>
       </c>
       <c r="B20" t="n">
-        <v>91812</v>
+        <v>91813</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 26837-2025 artfynd.xlsx
+++ b/artfynd/A 26837-2025 artfynd.xlsx
@@ -2054,7 +2054,7 @@
         <v>129099749</v>
       </c>
       <c r="B15" t="n">
-        <v>97582</v>
+        <v>97583</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2342,32 +2342,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129099758</v>
+        <v>129099751</v>
       </c>
       <c r="B18" t="n">
-        <v>78707</v>
+        <v>57831</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>103031</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>672113</v>
+        <v>672101</v>
       </c>
       <c r="R18" t="n">
-        <v>7394667</v>
+        <v>7394668</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2413,6 +2413,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2439,32 +2444,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129099751</v>
+        <v>129099758</v>
       </c>
       <c r="B19" t="n">
-        <v>57831</v>
+        <v>78707</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103031</v>
+        <v>353</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2474,10 +2479,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>672101</v>
+        <v>672113</v>
       </c>
       <c r="R19" t="n">
-        <v>7394668</v>
+        <v>7394667</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2510,11 +2515,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 26837-2025 artfynd.xlsx
+++ b/artfynd/A 26837-2025 artfynd.xlsx
@@ -1472,7 +1472,7 @@
         <v>129099750</v>
       </c>
       <c r="B9" t="n">
-        <v>91593</v>
+        <v>91596</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>129099761</v>
       </c>
       <c r="B10" t="n">
-        <v>78444</v>
+        <v>78446</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1663,32 +1663,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129099755</v>
+        <v>129099746</v>
       </c>
       <c r="B11" t="n">
-        <v>91813</v>
+        <v>90575</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>65</v>
+        <v>1962</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>671997</v>
+        <v>672131</v>
       </c>
       <c r="R11" t="n">
-        <v>7394521</v>
+        <v>7394641</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1760,32 +1760,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129099760</v>
+        <v>129099755</v>
       </c>
       <c r="B12" t="n">
-        <v>78707</v>
+        <v>91816</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>65</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1795,10 +1795,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>671996</v>
+        <v>671997</v>
       </c>
       <c r="R12" t="n">
-        <v>7394503</v>
+        <v>7394521</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1860,7 +1860,7 @@
         <v>129099756</v>
       </c>
       <c r="B13" t="n">
-        <v>78707</v>
+        <v>78709</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1954,10 +1954,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129099746</v>
+        <v>129099760</v>
       </c>
       <c r="B14" t="n">
-        <v>90572</v>
+        <v>78709</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1965,21 +1965,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>672131</v>
+        <v>671996</v>
       </c>
       <c r="R14" t="n">
-        <v>7394641</v>
+        <v>7394503</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2054,7 +2054,7 @@
         <v>129099749</v>
       </c>
       <c r="B15" t="n">
-        <v>97583</v>
+        <v>97587</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>129099753</v>
       </c>
       <c r="B16" t="n">
-        <v>91713</v>
+        <v>91716</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>129099745</v>
       </c>
       <c r="B17" t="n">
-        <v>91463</v>
+        <v>91466</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2342,32 +2342,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129099751</v>
+        <v>129099758</v>
       </c>
       <c r="B18" t="n">
-        <v>57831</v>
+        <v>78709</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103031</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>672101</v>
+        <v>672113</v>
       </c>
       <c r="R18" t="n">
-        <v>7394668</v>
+        <v>7394667</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2413,11 +2413,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2444,32 +2439,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129099758</v>
+        <v>129099751</v>
       </c>
       <c r="B19" t="n">
-        <v>78707</v>
+        <v>57831</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>353</v>
+        <v>103031</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2479,10 +2474,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>672113</v>
+        <v>672101</v>
       </c>
       <c r="R19" t="n">
-        <v>7394667</v>
+        <v>7394668</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2515,6 +2510,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2544,7 +2544,7 @@
         <v>129099754</v>
       </c>
       <c r="B20" t="n">
-        <v>91813</v>
+        <v>91816</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>129099759</v>
       </c>
       <c r="B21" t="n">
-        <v>78707</v>
+        <v>78709</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 26837-2025 artfynd.xlsx
+++ b/artfynd/A 26837-2025 artfynd.xlsx
@@ -1663,32 +1663,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129099746</v>
+        <v>129099755</v>
       </c>
       <c r="B11" t="n">
-        <v>90575</v>
+        <v>91816</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1962</v>
+        <v>65</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>672131</v>
+        <v>671997</v>
       </c>
       <c r="R11" t="n">
-        <v>7394641</v>
+        <v>7394521</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1760,32 +1760,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129099755</v>
+        <v>129099756</v>
       </c>
       <c r="B12" t="n">
-        <v>91816</v>
+        <v>78709</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>65</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1795,10 +1795,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>671997</v>
+        <v>672148</v>
       </c>
       <c r="R12" t="n">
-        <v>7394521</v>
+        <v>7394634</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1857,7 +1857,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129099756</v>
+        <v>129099760</v>
       </c>
       <c r="B13" t="n">
         <v>78709</v>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>672148</v>
+        <v>671996</v>
       </c>
       <c r="R13" t="n">
-        <v>7394634</v>
+        <v>7394503</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1954,32 +1954,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129099760</v>
+        <v>129099749</v>
       </c>
       <c r="B14" t="n">
-        <v>78709</v>
+        <v>97587</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>221941</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>671996</v>
+        <v>672300</v>
       </c>
       <c r="R14" t="n">
-        <v>7394503</v>
+        <v>7394545</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2051,32 +2051,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129099749</v>
+        <v>129099746</v>
       </c>
       <c r="B15" t="n">
-        <v>97587</v>
+        <v>90575</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221941</v>
+        <v>1962</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2086,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>672300</v>
+        <v>672131</v>
       </c>
       <c r="R15" t="n">
-        <v>7394545</v>
+        <v>7394641</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2148,32 +2148,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129099753</v>
+        <v>129099745</v>
       </c>
       <c r="B16" t="n">
-        <v>91716</v>
+        <v>91466</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1503</v>
+        <v>3242</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2183,10 +2183,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>672237</v>
+        <v>672062</v>
       </c>
       <c r="R16" t="n">
-        <v>7394626</v>
+        <v>7394679</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2245,32 +2245,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129099745</v>
+        <v>129099753</v>
       </c>
       <c r="B17" t="n">
-        <v>91466</v>
+        <v>91716</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3242</v>
+        <v>1503</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>672062</v>
+        <v>672237</v>
       </c>
       <c r="R17" t="n">
-        <v>7394679</v>
+        <v>7394626</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>

--- a/artfynd/A 26837-2025 artfynd.xlsx
+++ b/artfynd/A 26837-2025 artfynd.xlsx
@@ -1472,7 +1472,7 @@
         <v>129099750</v>
       </c>
       <c r="B9" t="n">
-        <v>91596</v>
+        <v>91598</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>129099761</v>
       </c>
       <c r="B10" t="n">
-        <v>78446</v>
+        <v>78447</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1663,32 +1663,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129099755</v>
+        <v>129099746</v>
       </c>
       <c r="B11" t="n">
-        <v>91816</v>
+        <v>90577</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>65</v>
+        <v>1962</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>671997</v>
+        <v>672131</v>
       </c>
       <c r="R11" t="n">
-        <v>7394521</v>
+        <v>7394641</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1760,32 +1760,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129099756</v>
+        <v>129099755</v>
       </c>
       <c r="B12" t="n">
-        <v>78709</v>
+        <v>91818</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>65</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1795,10 +1795,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>672148</v>
+        <v>671997</v>
       </c>
       <c r="R12" t="n">
-        <v>7394634</v>
+        <v>7394521</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1860,7 +1860,7 @@
         <v>129099760</v>
       </c>
       <c r="B13" t="n">
-        <v>78709</v>
+        <v>78710</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1954,32 +1954,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129099749</v>
+        <v>129099756</v>
       </c>
       <c r="B14" t="n">
-        <v>97587</v>
+        <v>78710</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221941</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>672300</v>
+        <v>672148</v>
       </c>
       <c r="R14" t="n">
-        <v>7394545</v>
+        <v>7394634</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2051,32 +2051,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129099746</v>
+        <v>129099749</v>
       </c>
       <c r="B15" t="n">
-        <v>90575</v>
+        <v>97589</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1962</v>
+        <v>221941</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2086,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>672131</v>
+        <v>672300</v>
       </c>
       <c r="R15" t="n">
-        <v>7394641</v>
+        <v>7394545</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2148,32 +2148,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129099745</v>
+        <v>129099753</v>
       </c>
       <c r="B16" t="n">
-        <v>91466</v>
+        <v>91718</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3242</v>
+        <v>1503</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2183,10 +2183,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>672062</v>
+        <v>672237</v>
       </c>
       <c r="R16" t="n">
-        <v>7394679</v>
+        <v>7394626</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2245,32 +2245,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129099753</v>
+        <v>129099745</v>
       </c>
       <c r="B17" t="n">
-        <v>91716</v>
+        <v>91468</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1503</v>
+        <v>3242</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>672237</v>
+        <v>672062</v>
       </c>
       <c r="R17" t="n">
-        <v>7394626</v>
+        <v>7394679</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2342,32 +2342,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129099758</v>
+        <v>129099751</v>
       </c>
       <c r="B18" t="n">
-        <v>78709</v>
+        <v>57831</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>103031</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>672113</v>
+        <v>672101</v>
       </c>
       <c r="R18" t="n">
-        <v>7394667</v>
+        <v>7394668</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2413,6 +2413,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2439,32 +2444,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129099751</v>
+        <v>129099758</v>
       </c>
       <c r="B19" t="n">
-        <v>57831</v>
+        <v>78710</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103031</v>
+        <v>353</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2474,10 +2479,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>672101</v>
+        <v>672113</v>
       </c>
       <c r="R19" t="n">
-        <v>7394668</v>
+        <v>7394667</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2510,11 +2515,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2544,7 +2544,7 @@
         <v>129099754</v>
       </c>
       <c r="B20" t="n">
-        <v>91816</v>
+        <v>91818</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>129099759</v>
       </c>
       <c r="B21" t="n">
-        <v>78709</v>
+        <v>78710</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 26837-2025 artfynd.xlsx
+++ b/artfynd/A 26837-2025 artfynd.xlsx
@@ -1472,7 +1472,7 @@
         <v>129099750</v>
       </c>
       <c r="B9" t="n">
-        <v>91598</v>
+        <v>91602</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>129099746</v>
       </c>
       <c r="B11" t="n">
-        <v>90577</v>
+        <v>90581</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>129099755</v>
       </c>
       <c r="B12" t="n">
-        <v>91818</v>
+        <v>91822</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129099760</v>
+        <v>129099756</v>
       </c>
       <c r="B13" t="n">
         <v>78710</v>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>671996</v>
+        <v>672148</v>
       </c>
       <c r="R13" t="n">
-        <v>7394503</v>
+        <v>7394634</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1954,7 +1954,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129099756</v>
+        <v>129099760</v>
       </c>
       <c r="B14" t="n">
         <v>78710</v>
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>672148</v>
+        <v>671996</v>
       </c>
       <c r="R14" t="n">
-        <v>7394634</v>
+        <v>7394503</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2054,7 +2054,7 @@
         <v>129099749</v>
       </c>
       <c r="B15" t="n">
-        <v>97589</v>
+        <v>97593</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>129099753</v>
       </c>
       <c r="B16" t="n">
-        <v>91718</v>
+        <v>91722</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>129099745</v>
       </c>
       <c r="B17" t="n">
-        <v>91468</v>
+        <v>91472</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2342,32 +2342,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129099751</v>
+        <v>129099758</v>
       </c>
       <c r="B18" t="n">
-        <v>57831</v>
+        <v>78710</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103031</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>672101</v>
+        <v>672113</v>
       </c>
       <c r="R18" t="n">
-        <v>7394668</v>
+        <v>7394667</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2413,11 +2413,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2444,32 +2439,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129099758</v>
+        <v>129099751</v>
       </c>
       <c r="B19" t="n">
-        <v>78710</v>
+        <v>57831</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>353</v>
+        <v>103031</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2479,10 +2474,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>672113</v>
+        <v>672101</v>
       </c>
       <c r="R19" t="n">
-        <v>7394667</v>
+        <v>7394668</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2515,6 +2510,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2544,7 +2544,7 @@
         <v>129099754</v>
       </c>
       <c r="B20" t="n">
-        <v>91818</v>
+        <v>91822</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 26837-2025 artfynd.xlsx
+++ b/artfynd/A 26837-2025 artfynd.xlsx
@@ -1472,7 +1472,7 @@
         <v>129099750</v>
       </c>
       <c r="B9" t="n">
-        <v>91602</v>
+        <v>91603</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>129099746</v>
       </c>
       <c r="B11" t="n">
-        <v>90581</v>
+        <v>90582</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1760,32 +1760,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129099755</v>
+        <v>129099749</v>
       </c>
       <c r="B12" t="n">
-        <v>91822</v>
+        <v>97601</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>65</v>
+        <v>221941</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1795,10 +1795,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>671997</v>
+        <v>672300</v>
       </c>
       <c r="R12" t="n">
-        <v>7394521</v>
+        <v>7394545</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1857,32 +1857,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129099756</v>
+        <v>129099755</v>
       </c>
       <c r="B13" t="n">
-        <v>78710</v>
+        <v>91823</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>65</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>672148</v>
+        <v>671997</v>
       </c>
       <c r="R13" t="n">
-        <v>7394634</v>
+        <v>7394521</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2051,32 +2051,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129099749</v>
+        <v>129099756</v>
       </c>
       <c r="B15" t="n">
-        <v>97593</v>
+        <v>78710</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221941</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2086,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>672300</v>
+        <v>672148</v>
       </c>
       <c r="R15" t="n">
-        <v>7394545</v>
+        <v>7394634</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2151,7 +2151,7 @@
         <v>129099753</v>
       </c>
       <c r="B16" t="n">
-        <v>91722</v>
+        <v>91723</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>129099745</v>
       </c>
       <c r="B17" t="n">
-        <v>91472</v>
+        <v>91473</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
         <v>129099754</v>
       </c>
       <c r="B20" t="n">
-        <v>91822</v>
+        <v>91823</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 26837-2025 artfynd.xlsx
+++ b/artfynd/A 26837-2025 artfynd.xlsx
@@ -1760,32 +1760,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129099749</v>
+        <v>129099755</v>
       </c>
       <c r="B12" t="n">
-        <v>97601</v>
+        <v>91823</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221941</v>
+        <v>65</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1795,10 +1795,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>672300</v>
+        <v>671997</v>
       </c>
       <c r="R12" t="n">
-        <v>7394545</v>
+        <v>7394521</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1857,32 +1857,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129099755</v>
+        <v>129099760</v>
       </c>
       <c r="B13" t="n">
-        <v>91823</v>
+        <v>78710</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>65</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>671997</v>
+        <v>671996</v>
       </c>
       <c r="R13" t="n">
-        <v>7394521</v>
+        <v>7394503</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1954,7 +1954,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129099760</v>
+        <v>129099756</v>
       </c>
       <c r="B14" t="n">
         <v>78710</v>
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>671996</v>
+        <v>672148</v>
       </c>
       <c r="R14" t="n">
-        <v>7394503</v>
+        <v>7394634</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2051,32 +2051,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129099756</v>
+        <v>129099749</v>
       </c>
       <c r="B15" t="n">
-        <v>78710</v>
+        <v>97601</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>221941</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2086,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>672148</v>
+        <v>672300</v>
       </c>
       <c r="R15" t="n">
-        <v>7394634</v>
+        <v>7394545</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>

--- a/artfynd/A 26837-2025 artfynd.xlsx
+++ b/artfynd/A 26837-2025 artfynd.xlsx
@@ -1663,32 +1663,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129099746</v>
+        <v>129099749</v>
       </c>
       <c r="B11" t="n">
-        <v>90582</v>
+        <v>97601</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1962</v>
+        <v>221941</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>672131</v>
+        <v>672300</v>
       </c>
       <c r="R11" t="n">
-        <v>7394641</v>
+        <v>7394545</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1760,32 +1760,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129099755</v>
+        <v>129099746</v>
       </c>
       <c r="B12" t="n">
-        <v>91823</v>
+        <v>90582</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>65</v>
+        <v>1962</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1795,10 +1795,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>671997</v>
+        <v>672131</v>
       </c>
       <c r="R12" t="n">
-        <v>7394521</v>
+        <v>7394641</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1857,32 +1857,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129099760</v>
+        <v>129099755</v>
       </c>
       <c r="B13" t="n">
-        <v>78710</v>
+        <v>91823</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>65</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>671996</v>
+        <v>671997</v>
       </c>
       <c r="R13" t="n">
-        <v>7394503</v>
+        <v>7394521</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1954,7 +1954,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129099756</v>
+        <v>129099760</v>
       </c>
       <c r="B14" t="n">
         <v>78710</v>
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>672148</v>
+        <v>671996</v>
       </c>
       <c r="R14" t="n">
-        <v>7394634</v>
+        <v>7394503</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2051,32 +2051,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129099749</v>
+        <v>129099756</v>
       </c>
       <c r="B15" t="n">
-        <v>97601</v>
+        <v>78710</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221941</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2086,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>672300</v>
+        <v>672148</v>
       </c>
       <c r="R15" t="n">
-        <v>7394545</v>
+        <v>7394634</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>

--- a/artfynd/A 26837-2025 artfynd.xlsx
+++ b/artfynd/A 26837-2025 artfynd.xlsx
@@ -1472,7 +1472,7 @@
         <v>129099750</v>
       </c>
       <c r="B9" t="n">
-        <v>91603</v>
+        <v>91606</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1663,32 +1663,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129099749</v>
+        <v>129099755</v>
       </c>
       <c r="B11" t="n">
-        <v>97601</v>
+        <v>91826</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221941</v>
+        <v>65</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>672300</v>
+        <v>671997</v>
       </c>
       <c r="R11" t="n">
-        <v>7394545</v>
+        <v>7394521</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1763,7 +1763,7 @@
         <v>129099746</v>
       </c>
       <c r="B12" t="n">
-        <v>90582</v>
+        <v>90585</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1857,32 +1857,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129099755</v>
+        <v>129099760</v>
       </c>
       <c r="B13" t="n">
-        <v>91823</v>
+        <v>78710</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>65</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>671997</v>
+        <v>671996</v>
       </c>
       <c r="R13" t="n">
-        <v>7394521</v>
+        <v>7394503</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1954,7 +1954,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129099760</v>
+        <v>129099756</v>
       </c>
       <c r="B14" t="n">
         <v>78710</v>
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>671996</v>
+        <v>672148</v>
       </c>
       <c r="R14" t="n">
-        <v>7394503</v>
+        <v>7394634</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2051,32 +2051,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129099756</v>
+        <v>129099749</v>
       </c>
       <c r="B15" t="n">
-        <v>78710</v>
+        <v>97604</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>221941</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2086,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>672148</v>
+        <v>672300</v>
       </c>
       <c r="R15" t="n">
-        <v>7394634</v>
+        <v>7394545</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2151,7 +2151,7 @@
         <v>129099753</v>
       </c>
       <c r="B16" t="n">
-        <v>91723</v>
+        <v>91726</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>129099745</v>
       </c>
       <c r="B17" t="n">
-        <v>91473</v>
+        <v>91476</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
         <v>129099754</v>
       </c>
       <c r="B20" t="n">
-        <v>91823</v>
+        <v>91826</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 26837-2025 artfynd.xlsx
+++ b/artfynd/A 26837-2025 artfynd.xlsx
@@ -1663,32 +1663,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129099755</v>
+        <v>129099760</v>
       </c>
       <c r="B11" t="n">
-        <v>91826</v>
+        <v>78710</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>65</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>671997</v>
+        <v>671996</v>
       </c>
       <c r="R11" t="n">
-        <v>7394521</v>
+        <v>7394503</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1760,32 +1760,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129099746</v>
+        <v>129099755</v>
       </c>
       <c r="B12" t="n">
-        <v>90585</v>
+        <v>91826</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1962</v>
+        <v>65</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1795,10 +1795,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>672131</v>
+        <v>671997</v>
       </c>
       <c r="R12" t="n">
-        <v>7394641</v>
+        <v>7394521</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1857,10 +1857,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129099760</v>
+        <v>129099746</v>
       </c>
       <c r="B13" t="n">
-        <v>78710</v>
+        <v>90585</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1868,21 +1868,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>1962</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>671996</v>
+        <v>672131</v>
       </c>
       <c r="R13" t="n">
-        <v>7394503</v>
+        <v>7394641</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>

--- a/artfynd/A 26837-2025 artfynd.xlsx
+++ b/artfynd/A 26837-2025 artfynd.xlsx
@@ -1663,32 +1663,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129099760</v>
+        <v>129099749</v>
       </c>
       <c r="B11" t="n">
-        <v>78710</v>
+        <v>97604</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>221941</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>671996</v>
+        <v>672300</v>
       </c>
       <c r="R11" t="n">
-        <v>7394503</v>
+        <v>7394545</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1760,32 +1760,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129099755</v>
+        <v>129099746</v>
       </c>
       <c r="B12" t="n">
-        <v>91826</v>
+        <v>90585</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>65</v>
+        <v>1962</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1795,10 +1795,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>671997</v>
+        <v>672131</v>
       </c>
       <c r="R12" t="n">
-        <v>7394521</v>
+        <v>7394641</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1857,32 +1857,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129099746</v>
+        <v>129099755</v>
       </c>
       <c r="B13" t="n">
-        <v>90585</v>
+        <v>91826</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1962</v>
+        <v>65</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>672131</v>
+        <v>671997</v>
       </c>
       <c r="R13" t="n">
-        <v>7394641</v>
+        <v>7394521</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1954,7 +1954,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129099756</v>
+        <v>129099760</v>
       </c>
       <c r="B14" t="n">
         <v>78710</v>
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>672148</v>
+        <v>671996</v>
       </c>
       <c r="R14" t="n">
-        <v>7394634</v>
+        <v>7394503</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2051,32 +2051,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129099749</v>
+        <v>129099756</v>
       </c>
       <c r="B15" t="n">
-        <v>97604</v>
+        <v>78710</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221941</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2086,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>672300</v>
+        <v>672148</v>
       </c>
       <c r="R15" t="n">
-        <v>7394545</v>
+        <v>7394634</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2148,32 +2148,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129099753</v>
+        <v>129099745</v>
       </c>
       <c r="B16" t="n">
-        <v>91726</v>
+        <v>91476</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1503</v>
+        <v>3242</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2183,10 +2183,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>672237</v>
+        <v>672062</v>
       </c>
       <c r="R16" t="n">
-        <v>7394626</v>
+        <v>7394679</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2245,32 +2245,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129099745</v>
+        <v>129099753</v>
       </c>
       <c r="B17" t="n">
-        <v>91476</v>
+        <v>91726</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3242</v>
+        <v>1503</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>672062</v>
+        <v>672237</v>
       </c>
       <c r="R17" t="n">
-        <v>7394679</v>
+        <v>7394626</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>

--- a/artfynd/A 26837-2025 artfynd.xlsx
+++ b/artfynd/A 26837-2025 artfynd.xlsx
@@ -1663,32 +1663,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129099749</v>
+        <v>129099755</v>
       </c>
       <c r="B11" t="n">
-        <v>97604</v>
+        <v>91826</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221941</v>
+        <v>65</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>672300</v>
+        <v>671997</v>
       </c>
       <c r="R11" t="n">
-        <v>7394545</v>
+        <v>7394521</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1760,10 +1760,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129099746</v>
+        <v>129099760</v>
       </c>
       <c r="B12" t="n">
-        <v>90585</v>
+        <v>78710</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1771,21 +1771,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1795,10 +1795,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>672131</v>
+        <v>671996</v>
       </c>
       <c r="R12" t="n">
-        <v>7394641</v>
+        <v>7394503</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1857,32 +1857,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129099755</v>
+        <v>129099756</v>
       </c>
       <c r="B13" t="n">
-        <v>91826</v>
+        <v>78710</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>65</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>671997</v>
+        <v>672148</v>
       </c>
       <c r="R13" t="n">
-        <v>7394521</v>
+        <v>7394634</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1954,10 +1954,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129099760</v>
+        <v>129099746</v>
       </c>
       <c r="B14" t="n">
-        <v>78710</v>
+        <v>90585</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1965,21 +1965,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>1962</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>671996</v>
+        <v>672131</v>
       </c>
       <c r="R14" t="n">
-        <v>7394503</v>
+        <v>7394641</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2051,32 +2051,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129099756</v>
+        <v>129099749</v>
       </c>
       <c r="B15" t="n">
-        <v>78710</v>
+        <v>97604</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>221941</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2086,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>672148</v>
+        <v>672300</v>
       </c>
       <c r="R15" t="n">
-        <v>7394634</v>
+        <v>7394545</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>

--- a/artfynd/A 26837-2025 artfynd.xlsx
+++ b/artfynd/A 26837-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>55964001</v>
+        <v>129099755</v>
       </c>
       <c r="B2" t="n">
-        <v>89545</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1503</v>
+        <v>65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>672170.0758357489</v>
+        <v>671997</v>
       </c>
       <c r="R2" t="n">
-        <v>7394345.985427582</v>
+        <v>7394521</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2012-08-15</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2012-08-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,41 +756,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>Tallåga</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Tallåga</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sture Westerberg, Camilla Carlsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>74694918</v>
+        <v>74694314</v>
       </c>
       <c r="B3" t="n">
-        <v>90841</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>671973.1927532288</v>
+        <v>671973</v>
       </c>
       <c r="R3" t="n">
-        <v>7394510.938353892</v>
+        <v>7394511</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2018-06-08</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-06-09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2018-06-08</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-06-09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>74694324</v>
+        <v>74694318</v>
       </c>
       <c r="B4" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -949,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>672116.9476063239</v>
+        <v>671963</v>
       </c>
       <c r="R4" t="n">
-        <v>7394449.808859444</v>
+        <v>7394539</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,19 +937,9 @@
           <t>2018-06-08</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2018-06-08</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>74694319</v>
+        <v>129099759</v>
       </c>
       <c r="B5" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1057,17 +997,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Luovos, Lu lm</t>
+          <t>Luvos, Lu lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>672069.9500094345</v>
+        <v>671976</v>
       </c>
       <c r="R5" t="n">
-        <v>7394532.106823651</v>
+        <v>7394598</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,22 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2018-06-08</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2018-06-08</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,27 +1051,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Frida Snell, Frédéric Forsmark</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>74694917</v>
+        <v>129099760</v>
       </c>
       <c r="B6" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1169,17 +1094,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Luovos, Lu lm</t>
+          <t>Luvos, Lu lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>671973.1927532288</v>
+        <v>671996</v>
       </c>
       <c r="R6" t="n">
-        <v>7394510.938353892</v>
+        <v>7394503</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1203,22 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2018-06-09</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2018-06-09</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,27 +1148,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Frida Snell, Frédéric Forsmark</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>74694919</v>
+        <v>74694316</v>
       </c>
       <c r="B7" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1261,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1285,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>671963.0718681454</v>
+        <v>671973</v>
       </c>
       <c r="R7" t="n">
-        <v>7394538.982404954</v>
+        <v>7394511</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1318,19 +1228,9 @@
           <t>2018-06-08</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2018-06-08</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>74694921</v>
+        <v>129099750</v>
       </c>
       <c r="B8" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1373,37 +1268,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Luovos, Lu lm</t>
+          <t>Luvos, Lu lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>672327.8724116108</v>
+        <v>672002</v>
       </c>
       <c r="R8" t="n">
-        <v>7394590.02696037</v>
+        <v>7394637</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1427,22 +1322,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2018-06-08</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2018-06-08</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1457,22 +1342,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Frida Snell, Frédéric Forsmark</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129099750</v>
+        <v>129099762</v>
       </c>
       <c r="B9" t="n">
-        <v>91606</v>
+        <v>78730</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1480,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2079</v>
+        <v>6437</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1504,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>672002</v>
+        <v>671973</v>
       </c>
       <c r="R9" t="n">
-        <v>7394637</v>
+        <v>7394634</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1566,32 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129099761</v>
+        <v>129099754</v>
       </c>
       <c r="B10" t="n">
-        <v>78447</v>
+        <v>92183</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6437</v>
+        <v>65</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1601,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>672262</v>
+        <v>672301</v>
       </c>
       <c r="R10" t="n">
-        <v>7394602</v>
+        <v>7394541</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1663,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129099755</v>
+        <v>112562</v>
       </c>
       <c r="B11" t="n">
-        <v>91826</v>
+        <v>78993</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>65</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1698,13 +1583,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>671997</v>
+        <v>672111</v>
       </c>
       <c r="R11" t="n">
-        <v>7394521</v>
+        <v>7394286</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1728,12 +1613,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2012-08-16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2012-08-16</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1744,26 +1629,31 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>som förra punkten. Mkt hänglav. Äldre trädskikt. Överlag sparsamt m död ved</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Via Sture Westerberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129099760</v>
+        <v>74694319</v>
       </c>
       <c r="B12" t="n">
-        <v>78710</v>
+        <v>78993</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1791,17 +1681,17 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Luvos, Lu lm</t>
+          <t>Luovos, Lu lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>671996</v>
+        <v>672070</v>
       </c>
       <c r="R12" t="n">
-        <v>7394503</v>
+        <v>7394532</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1825,12 +1715,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2018-06-08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2018-06-08</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1845,22 +1735,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Frida Snell, Frédéric Forsmark</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129099756</v>
+        <v>74694321</v>
       </c>
       <c r="B13" t="n">
-        <v>78710</v>
+        <v>78993</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1888,17 +1778,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Luvos, Lu lm</t>
+          <t>Luovos, Lu lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>672148</v>
+        <v>672328</v>
       </c>
       <c r="R13" t="n">
-        <v>7394634</v>
+        <v>7394590</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1922,12 +1812,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2018-06-08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2018-06-08</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1942,22 +1832,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Frida Snell, Frédéric Forsmark</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129099746</v>
+        <v>74694324</v>
       </c>
       <c r="B14" t="n">
-        <v>90585</v>
+        <v>78993</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1965,37 +1855,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Luvos, Lu lm</t>
+          <t>Luovos, Lu lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>672131</v>
+        <v>672117</v>
       </c>
       <c r="R14" t="n">
-        <v>7394641</v>
+        <v>7394450</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2019,12 +1909,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2018-06-08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2018-06-08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2039,44 +1929,44 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Frida Snell, Frédéric Forsmark</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129099749</v>
+        <v>129099756</v>
       </c>
       <c r="B15" t="n">
-        <v>97604</v>
+        <v>78993</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221941</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2086,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>672300</v>
+        <v>672148</v>
       </c>
       <c r="R15" t="n">
-        <v>7394545</v>
+        <v>7394634</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2148,10 +2038,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129099745</v>
+        <v>129099758</v>
       </c>
       <c r="B16" t="n">
-        <v>91476</v>
+        <v>78993</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2159,21 +2049,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3242</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2183,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>672062</v>
+        <v>672113</v>
       </c>
       <c r="R16" t="n">
-        <v>7394679</v>
+        <v>7394667</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2245,10 +2135,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129099753</v>
+        <v>55964001</v>
       </c>
       <c r="B17" t="n">
-        <v>91726</v>
+        <v>92083</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2280,13 +2170,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>672237</v>
+        <v>672170</v>
       </c>
       <c r="R17" t="n">
-        <v>7394626</v>
+        <v>7394346</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2310,12 +2200,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2012-08-15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2012-08-15</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2326,48 +2216,58 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>Tallåga</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Tallåga</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Sture Westerberg, Camilla Carlsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129099758</v>
+        <v>129099753</v>
       </c>
       <c r="B18" t="n">
-        <v>78710</v>
+        <v>92083</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>1503</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2377,10 +2277,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>672113</v>
+        <v>672237</v>
       </c>
       <c r="R18" t="n">
-        <v>7394667</v>
+        <v>7394626</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2439,32 +2339,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129099751</v>
+        <v>129099746</v>
       </c>
       <c r="B19" t="n">
-        <v>57831</v>
+        <v>90932</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103031</v>
+        <v>1962</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2474,10 +2374,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>672101</v>
+        <v>672131</v>
       </c>
       <c r="R19" t="n">
-        <v>7394668</v>
+        <v>7394641</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2510,11 +2410,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2541,32 +2436,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129099754</v>
+        <v>129099745</v>
       </c>
       <c r="B20" t="n">
-        <v>91826</v>
+        <v>91831</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>65</v>
+        <v>3242</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2576,10 +2471,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>672301</v>
+        <v>672062</v>
       </c>
       <c r="R20" t="n">
-        <v>7394541</v>
+        <v>7394679</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2638,10 +2533,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129099759</v>
+        <v>129099761</v>
       </c>
       <c r="B21" t="n">
-        <v>78710</v>
+        <v>78730</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2649,21 +2544,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2673,10 +2568,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>671976</v>
+        <v>672262</v>
       </c>
       <c r="R21" t="n">
-        <v>7394598</v>
+        <v>7394602</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2732,6 +2627,205 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129099751</v>
+      </c>
+      <c r="B22" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Luvos, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>672101</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7394668</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129099749</v>
+      </c>
+      <c r="B23" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Luvos, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>672300</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7394545</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26837-2025 artfynd.xlsx
+++ b/artfynd/A 26837-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129099754</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129099755</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112562</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,6 +1085,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74694314</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74694318</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1259,6 +1289,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74694319</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1356,6 +1391,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74694321</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1453,6 +1493,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74694324</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1550,6 +1595,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129099756</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1647,6 +1697,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129099758</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1744,6 +1799,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129099759</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1841,6 +1901,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129099760</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1948,6 +2013,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55964001</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2045,6 +2115,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129099753</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2142,6 +2217,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129099746</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2239,6 +2319,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74694316</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2336,6 +2421,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129099750</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2433,6 +2523,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129099745</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2530,6 +2625,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129099761</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2627,6 +2727,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129099762</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2729,6 +2834,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129099751</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2826,8 +2936,37 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129099749</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>